--- a/www/download/IND.gross_output.s.us.WIOD16.xlsx
+++ b/www/download/IND.gross_output.s.us.WIOD16.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.796</t>
+          <t>795738.228276079</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.758</t>
+          <t>758249.740972326</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.847</t>
+          <t>846925.503179066</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1100133.62665529</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1329886.73772367</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>1.484</t>
+          <t>1484266.35382978</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>1.588</t>
+          <t>1588225.32534999</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>1.918</t>
+          <t>1917733.661974</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2.097</t>
+          <t>2097357.72144838</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>1.987</t>
+          <t>1986523.01527065</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2.484</t>
+          <t>2484151.78350897</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>2.931</t>
+          <t>2931207.75149672</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2.962</t>
+          <t>2962485.3652</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2.874</t>
+          <t>2874155.75622</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2.724</t>
+          <t>2723737.21668623</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.334</t>
+          <t>334335.25704</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.339</t>
+          <t>339350.18392</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.368</t>
+          <t>368345.61984</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.454</t>
+          <t>454301.68448</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0.528</t>
+          <t>527502.29007</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>0.561</t>
+          <t>561338.16882</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0.609</t>
+          <t>608876.97796</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>0.708</t>
+          <t>707979.05725</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>0.804</t>
+          <t>803876.47684</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>0.726</t>
+          <t>725903.85384</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>0.721</t>
+          <t>721151.50203</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>0.805</t>
+          <t>805059.1632</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>0.765</t>
+          <t>764692.78864</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>0.803</t>
+          <t>803041.64145</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>809630.6777</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.492</t>
+          <t>492090.93976</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.496</t>
+          <t>496082.87072</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.526</t>
+          <t>525752.27616</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.635</t>
+          <t>635131.35728</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.744</t>
+          <t>743575.05908</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.782</t>
+          <t>781713.06642</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.846</t>
+          <t>845735.37092</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>979721.79725</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>1.103</t>
+          <t>1103384.30564</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.973</t>
+          <t>972813.99996</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0.997</t>
+          <t>997284.73671</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>1.129</t>
+          <t>1129381.6608</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1.058</t>
+          <t>1058281.92272</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>1.091</t>
+          <t>1091329.25382</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>1.111</t>
+          <t>1110756.4587</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>26598.84876</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>29159.2235189638</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>33196.0416481221</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>43155.8364414454</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>55599.0483943455</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>64677.15111</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>76558.3960060623</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.101</t>
+          <t>100872.166821269</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>122302.795360926</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>109314.52092</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>0.104</t>
+          <t>103788.731154545</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>121405.166527261</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>113977.624023257</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>115598.518222755</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>122872.506772056</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1150451.4285624</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.994</t>
+          <t>993535.107520598</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>939685.511931887</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1.021</t>
+          <t>1020845.03736714</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>1.228</t>
+          <t>1227682.98815445</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>1.635</t>
+          <t>1634664.59418755</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>1.985</t>
+          <t>1985416.78351458</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2490215.52872017</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>3.037</t>
+          <t>3036708.36723138</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2.872</t>
+          <t>2872494.31961956</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>3.752</t>
+          <t>3751500.56552</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>4.445</t>
+          <t>4445219.04552</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>4.207</t>
+          <t>4206527.84251</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>4.217</t>
+          <t>4216646.886183</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>4.104</t>
+          <t>4103501.78349504</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1.366</t>
+          <t>1365527.96228737</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1.356</t>
+          <t>1355973.66083594</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1380445.23205767</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>1.628</t>
+          <t>1627775.44447647</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>1.861</t>
+          <t>1860912.53771855</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2.119</t>
+          <t>2119134.07086209</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2.389</t>
+          <t>2388772.49507481</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2.642</t>
+          <t>2642017.00121568</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>2809910.53806106</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2.492</t>
+          <t>2492268.703248</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2.935</t>
+          <t>2935496.635278</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>3.251</t>
+          <t>3250588.81304</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>3.34</t>
+          <t>3340328.28866402</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>3.356</t>
+          <t>3356078.11922139</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>3.252</t>
+          <t>3252175.04021287</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>3.253</t>
+          <t>3253015.70227797</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3.521</t>
+          <t>3521177.91153665</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3.812</t>
+          <t>3812211.86576439</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>4.456</t>
+          <t>4455647.71315393</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>5.438</t>
+          <t>5437770.06408265</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>6.707</t>
+          <t>6707046.56430474</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>8.178</t>
+          <t>8177587.50590138</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>10.654</t>
+          <t>10654372.3158218</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>13.69</t>
+          <t>13689958.4413456</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>15.037</t>
+          <t>15036959.8810756</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>18.054</t>
+          <t>18053714.464996</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>22.609</t>
+          <t>22608922.70497</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>25.593</t>
+          <t>25593234.4224765</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>29.233</t>
+          <t>29232642.460012</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>31.745</t>
+          <t>31745102.4312362</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>17663.3882</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>18084.5165410274</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>19763.488076634</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>24850.31472</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>28880.0921413263</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>30791.3212220929</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>33766.8827217683</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>40105.9717238383</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>46766.3991117324</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>44133.1795034204</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>42607.7346783981</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>46063.3318177726</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>42409.3166015849</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>41653.3976637709</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>39448.2629837531</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.138</t>
+          <t>137783.3099452</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>151346.0164176</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.182</t>
+          <t>182446.193061</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>0.227</t>
+          <t>227352.7929276</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0.274</t>
+          <t>274328.951052</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>0.312</t>
+          <t>312337.707192</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>0.371</t>
+          <t>370516.8223576</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>0.456</t>
+          <t>456066.7381697</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>0.567</t>
+          <t>566629.3002162</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>0.467</t>
+          <t>467214.9208103</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>0.486</t>
+          <t>485891.697095</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>0.548</t>
+          <t>548193.7583843</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>0.492</t>
+          <t>491599.3975398</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>0.493</t>
+          <t>492524.4328098</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>0.493</t>
+          <t>492771.782905</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>3.462</t>
+          <t>3461853.2212</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>3460336.8848</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>3.636</t>
+          <t>3636377.6112</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>4.422</t>
+          <t>4422279.344</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>5.025</t>
+          <t>5025494.0729</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>5.185</t>
+          <t>5185113.9483</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>5.525</t>
+          <t>5525497.5748</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>6.376</t>
+          <t>6375749.647</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>7.076</t>
+          <t>7076454.1568</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>6.239</t>
+          <t>6239144.0408</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>6.332</t>
+          <t>6331706.2611</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>7.116</t>
+          <t>7115837.184</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>6.609</t>
+          <t>6608792.784</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>6.915</t>
+          <t>6914995.6923</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>7.067</t>
+          <t>7066740.533</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.274</t>
+          <t>273742.650192</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.279</t>
+          <t>278889.915829</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0.301</t>
+          <t>300689.346943</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>0.363</t>
+          <t>363470.157518</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0.417</t>
+          <t>416795.059737</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>450289.704924</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>0.492</t>
+          <t>492037.93254</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>0.569</t>
+          <t>568886.803756</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>0.642</t>
+          <t>642214.07382</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>559835.593455</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>0.554</t>
+          <t>553719.46551</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>0.606</t>
+          <t>606152.632302</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>0.581</t>
+          <t>580801.584792</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>0.601</t>
+          <t>601457.0229</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>0.615</t>
+          <t>614581.853431</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1.114</t>
+          <t>1114171.9296</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1180336.3168</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1.359</t>
+          <t>1359448.4592</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>1.751</t>
+          <t>1750924.5264</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2.091</t>
+          <t>2091361.6066</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2.309</t>
+          <t>2308764.7011</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2.578</t>
+          <t>2578264.1072</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>3.036</t>
+          <t>3036474.318</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>3.313</t>
+          <t>3313043.186</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2.865</t>
+          <t>2864772.746</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2.702</t>
+          <t>2702194.1955</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>2830211.616</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2.524</t>
+          <t>2524467.5456</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>2.549</t>
+          <t>2549224.2012</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2.568</t>
+          <t>2567905.476</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>11786.2372750432</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>13060.7993377414</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>15297.9866404659</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>20138.2232260324</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>24827.3330292857</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>28656.3510239008</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>34086.51278339</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>43944.4287437199</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>48629.5355227539</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>36981.5841510545</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>38925.1354716147</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>47853.4408140883</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>47221.2050453434</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>52216.6670370017</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>54483.1692395794</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.237</t>
+          <t>236980.0588</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.237</t>
+          <t>236684.69</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>0.255</t>
+          <t>254773.008</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.312</t>
+          <t>311602.6144</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.363</t>
+          <t>362604.3134</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.383</t>
+          <t>383159.1621</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.417</t>
+          <t>417431.7536</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.492</t>
+          <t>492128.7335</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.556</t>
+          <t>556474.2384</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.473</t>
+          <t>472521.9752</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>0.471</t>
+          <t>471053.0268</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>0.529</t>
+          <t>529475.04</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>0.496</t>
+          <t>496080.552</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>0.512</t>
+          <t>511779.3507</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>0.514</t>
+          <t>513657.8825</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2.415</t>
+          <t>2414723.5684</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2.452</t>
+          <t>2451820.5324</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2.646</t>
+          <t>2646301.3152</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>3.222</t>
+          <t>3221789.9504</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>3.706</t>
+          <t>3706355.5375</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>3.876</t>
+          <t>3875851.7226</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>4.128</t>
+          <t>4128007.2412</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>4749697.994</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>5.252</t>
+          <t>5251791.4432</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>4.722</t>
+          <t>4721921.05</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>4.697</t>
+          <t>4696735.0338</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>5.13</t>
+          <t>5130046.176</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>4.807</t>
+          <t>4806515.1728</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>5.004</t>
+          <t>5004462.7497</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>5020134.47832235</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2.754</t>
+          <t>2753696.94801</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2.733</t>
+          <t>2733398.31016</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2.982</t>
+          <t>2982311.53914</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>3.407</t>
+          <t>3407164.60152</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>4.027</t>
+          <t>4026986.9886</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>4.177</t>
+          <t>4176743.964</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>4.576</t>
+          <t>4576033.40775</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>5289599.5344</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>5.038</t>
+          <t>5038019.96732</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>4.188</t>
+          <t>4188352.32544</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>4.276</t>
+          <t>4275965.10708</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>4.597</t>
+          <t>4597391.3084</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>4.659</t>
+          <t>4659264.13744</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>4.808</t>
+          <t>4808146.66533</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>5.283</t>
+          <t>5283463.35134482</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.216</t>
+          <t>216384.626179433</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.223</t>
+          <t>222839.176974647</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.253</t>
+          <t>253427.303695132</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.325</t>
+          <t>324724.142117982</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.388</t>
+          <t>387847.130174357</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>399975.996473911</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.444</t>
+          <t>444439.543068724</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.518</t>
+          <t>517719.991568386</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0.568</t>
+          <t>568356.966791784</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0.524</t>
+          <t>524185.764184476</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>470137.276661896</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>449979.216539234</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>0.394</t>
+          <t>394295.267582509</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>0.383</t>
+          <t>383396.329357871</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>0.375</t>
+          <t>375244.052215509</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.099</t>
+          <t>98593.855818</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>110350.79851428</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>134515.43031312</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.168</t>
+          <t>167628.85878557</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.204</t>
+          <t>203622.5873409</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.227</t>
+          <t>227451.12632476</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>239637.48367748</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.286</t>
+          <t>286482.18051702</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.329</t>
+          <t>329371.23990971</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>260315.30083363</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>0.265</t>
+          <t>265080.12012944</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>0.292</t>
+          <t>292185.89576605</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>0.258</t>
+          <t>258209.98925234</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>270431.95398596</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>0.284</t>
+          <t>284429.54634624</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.353</t>
+          <t>352659.977508832</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.344</t>
+          <t>343818.891039101</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.424</t>
+          <t>424059.334916915</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.503</t>
+          <t>503277.12338178</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>550006.490494811</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.602</t>
+          <t>602121.477731851</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.766</t>
+          <t>765627.015501197</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.899</t>
+          <t>898556.51322495</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>1.069</t>
+          <t>1068647.62990199</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1119800.69253673</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1.444</t>
+          <t>1443519.27274689</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>1.712</t>
+          <t>1711859.33158715</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1759671.71259452</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>1.753</t>
+          <t>1752939.4422821</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>1.714</t>
+          <t>1714343.06732921</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>889777.384223659</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0.931</t>
+          <t>930507.62886154</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>0.983</t>
+          <t>983486.012994518</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>1.168</t>
+          <t>1168335.43124015</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>1.383</t>
+          <t>1382823.36808295</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>1.609</t>
+          <t>1608557.12264892</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1853972.07381421</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>2.352</t>
+          <t>2351594.12058147</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2.589</t>
+          <t>2588525.09056901</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2.636</t>
+          <t>2636498.48519716</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>3.338</t>
+          <t>3338037.48672886</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>3.866</t>
+          <t>3865701.52427261</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>3720169.29890541</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>3.781</t>
+          <t>3780995.42850508</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>3.984</t>
+          <t>3983527.12113965</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>0.204</t>
+          <t>204392.12584</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.223</t>
+          <t>222582.03504</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.257</t>
+          <t>256656.54864</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>0.334</t>
+          <t>334341.31808</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0.395</t>
+          <t>395322.11754</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>0.435</t>
+          <t>434691.89907</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>0.493</t>
+          <t>492880.38092</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>0.581</t>
+          <t>581314.8433</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>0.623</t>
+          <t>623311.8028</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>0.524</t>
+          <t>523515.8632</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>0.466</t>
+          <t>465506.82828</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>480215.2224</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>450359.91616</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>0.481</t>
+          <t>481233.58194</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>0.509</t>
+          <t>509477.093</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2.214</t>
+          <t>2213740.26544</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2.258</t>
+          <t>2258374.067</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2.456</t>
+          <t>2455603.48704</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>3.024</t>
+          <t>3023639.3432</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>3470152.36162</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>3.609</t>
+          <t>3609145.17249</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>3.835</t>
+          <t>3835137.03448</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>4.399</t>
+          <t>4399257.3066</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>4.805</t>
+          <t>4805338.1926</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>4.159</t>
+          <t>4158508.3276</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>4.134</t>
+          <t>4133509.79796</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>4.475</t>
+          <t>4475042.9424</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>4.025</t>
+          <t>4024546.7064</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>4.098</t>
+          <t>4098209.01204</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>4.075</t>
+          <t>4075402.11906248</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>8.691</t>
+          <t>8691188.71794</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>7.607</t>
+          <t>7607273.101566</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>7.256</t>
+          <t>7255717.057897</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>7.845</t>
+          <t>7844807.361578</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>8.566</t>
+          <t>8566025.20592</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>8.633</t>
+          <t>8632723.076474</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>8.378</t>
+          <t>8377589.479347</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>8.489</t>
+          <t>8489260.46098099</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>9.691</t>
+          <t>9691283.5756</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>9.355</t>
+          <t>9354837.54048</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>10.317</t>
+          <t>10317384.1940403</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>11.271</t>
+          <t>11271277.3727482</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>11.351</t>
+          <t>11351477.6356733</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>9.378</t>
+          <t>9378218.96326445</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>8.669</t>
+          <t>8668735.69674184</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>1.176</t>
+          <t>1175975.8116288</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1100066.474877</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>1.248</t>
+          <t>1248189.0194004</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>1.403</t>
+          <t>1402883.109684</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1629694.6278162</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>1.946</t>
+          <t>1945950.5879686</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>2.234</t>
+          <t>2233897.770184</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>2.516</t>
+          <t>2516486.668439</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2.456</t>
+          <t>2456129.258247</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2.145</t>
+          <t>2144878.2888442</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2.638</t>
+          <t>2638334.07438</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>3.041</t>
+          <t>3040670.68324</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>3.084</t>
+          <t>3083803.3577923</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>3.202</t>
+          <t>3201879.2379372</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>3.404</t>
+          <t>3403854.39562871</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>19372.3787848133</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>20588.3498919947</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>24090.62757454</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>31388.2037276302</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>38656.80469</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>45498.4464263389</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>53332.4778821863</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>68467.0647980007</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>87005.8837681186</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>63960.5735342206</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>65754.9255570678</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>78302.088</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>76309.2426354663</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>82759.8453207151</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>85667.7869697813</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>50505.3760674947</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>50980.8963623003</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>55018.97952</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>68137.86924379</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.085</t>
+          <t>84902.9774229963</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>96571.2292327918</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.118</t>
+          <t>117965.874572581</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.148</t>
+          <t>147783.756</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>162520.16424</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.138</t>
+          <t>138028.710634105</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>0.152</t>
+          <t>152441.88981628</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>0.172</t>
+          <t>172104.974100951</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>0.168</t>
+          <t>167672.226133539</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>0.189</t>
+          <t>189168.449694447</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>0.212</t>
+          <t>211968.19051659</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>15754.5670253981</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>16410.0788</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>18409.4136</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>23057.0232321462</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>28900.4797995319</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>33959.7685429513</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>44468.6776307872</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>61655.7183253122</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>71521.3882057261</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>51904.869698414</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>49324.52448</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>58585.339919238</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>59343.4680153342</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>63011.0093653305</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>64725.6628781127</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>1.093</t>
+          <t>1093021.60297776</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1.145</t>
+          <t>1144825.36889574</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>1.188</t>
+          <t>1187559.05305344</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>1.164</t>
+          <t>1163601.03658961</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>1.265</t>
+          <t>1264788.82493296</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>1.435</t>
+          <t>1435254.98091125</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>1.602</t>
+          <t>1601970.15663729</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>1.734</t>
+          <t>1734393.61109023</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>1.875</t>
+          <t>1874876.70507398</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>1.473</t>
+          <t>1473112.9152775</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1.741</t>
+          <t>1741137.42896123</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1960922.18806455</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2000442.35376764</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>2.104</t>
+          <t>2104457.9027096</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2130489.33858109</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>9348.10856948186</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>8894.77516214479</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>9645.32939037522</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>11758.9497402579</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>13115.1277074974</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>14064.4587028943</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>16049.6943819924</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>19192.3312062274</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>23955.175567226</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>22662.8580002929</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>23315.1209811747</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>26274.5104106667</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>25867.0448644158</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>27688.114110653</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>28914.9279802297</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>0.776</t>
+          <t>775867.4092</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.796</t>
+          <t>796432.0032</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>860237.8512</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>1.044</t>
+          <t>1043978.824</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1189867.4718</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1250410.0752</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>1.338</t>
+          <t>1338182.0676</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>1.552</t>
+          <t>1551741.7725</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>1.753</t>
+          <t>1752836.1956</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>1.593</t>
+          <t>1593033.1604</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1.563</t>
+          <t>1562899.5468</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>1.724</t>
+          <t>1723872.288</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>1.613</t>
+          <t>1613444.1312</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>1.659</t>
+          <t>1659468.9186</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>1.671</t>
+          <t>1671177.2755</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>0.335</t>
+          <t>334974.60193125</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.375</t>
+          <t>374552.868613436</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.385</t>
+          <t>384544.0803536</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>0.424</t>
+          <t>424463.27904</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0.509</t>
+          <t>508946.375127</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>0.603</t>
+          <t>603394.775417</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>0.696</t>
+          <t>695532.495768</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>0.885</t>
+          <t>884827.945253</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>1.108</t>
+          <t>1108469.481984</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>0.874</t>
+          <t>873733.618187</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>960207.773196</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>1.084</t>
+          <t>1083831.10569</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1.012</t>
+          <t>1012234.018928</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>1.061</t>
+          <t>1060614.828234</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>1.105</t>
+          <t>1105443.87064394</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>0.226</t>
+          <t>226473.00048</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.232</t>
+          <t>232029.972363258</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.251</t>
+          <t>250750.41054124</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>0.304</t>
+          <t>303967.118019651</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0.351</t>
+          <t>351427.49873</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>0.366</t>
+          <t>365509.673558174</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>0.384</t>
+          <t>384162.453956551</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>0.445</t>
+          <t>444873.8935</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>0.497</t>
+          <t>496893.911699466</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>0.444</t>
+          <t>444009.495613162</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>0.435</t>
+          <t>435458.424624214</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>0.455</t>
+          <t>454933.089718619</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>0.398</t>
+          <t>397564.147927618</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>0.409</t>
+          <t>408870.452606089</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>0.414</t>
+          <t>414280.893686788</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>72755.1894132827</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>78810.8917631496</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>89408.4041190576</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>0.115</t>
+          <t>115064.161426121</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0.149</t>
+          <t>148625.144013846</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>0.188</t>
+          <t>188250.323238368</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>0.234</t>
+          <t>233670.407930931</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>0.318</t>
+          <t>318100.594525816</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>0.393</t>
+          <t>392981.918667009</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>319526.976473395</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>0.327</t>
+          <t>327039.628131043</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>0.371</t>
+          <t>371363.491541286</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>0.352</t>
+          <t>351813.226932782</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>0.386</t>
+          <t>385683.095773541</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>0.398</t>
+          <t>398280.094568145</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>0.446</t>
+          <t>446270.03779127</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.546</t>
+          <t>546091.11494636</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.608</t>
+          <t>607515.54866235</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>0.759</t>
+          <t>758684.08618872</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>1.024</t>
+          <t>1023657.84825538</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>1.309</t>
+          <t>1309118.82232761</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>1.701</t>
+          <t>1700894.99321385</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>2.259</t>
+          <t>2258991.98837725</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>2.892</t>
+          <t>2891627.8589355</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>2.186</t>
+          <t>2185970.34762696</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2.635</t>
+          <t>2635097.87335472</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>3.263</t>
+          <t>3262680.41250156</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>3.416</t>
+          <t>3415630.89062014</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>3.631</t>
+          <t>3630523.90256947</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>3.381</t>
+          <t>3381079.3674049</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>47953.6234255736</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>49500.2297137135</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>57598.1241747581</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>78315.0614172103</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>95245.6109264023</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>0.107</t>
+          <t>107333.35899</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>129506.065420792</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>0.174</t>
+          <t>174225.797122471</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>0.223</t>
+          <t>222650.928757272</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>0.194</t>
+          <t>193954.467087264</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>200018.03661</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>0.228</t>
+          <t>228356.727199755</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>0.218</t>
+          <t>218230.673529046</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>0.227</t>
+          <t>226612.921739587</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>0.229</t>
+          <t>229289.13625</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>38579.1617399267</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>39325.6364436374</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>44418.3104480493</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>55448.700313368</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>65225.4463534792</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>69632.8395131956</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>77659.5813408991</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>96517.9437891536</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>111674.278972107</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>95346.169903852</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>93316.8537318963</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>99911.7744</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>89210.6965287903</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>91214.97048</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>94237.6435321417</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>0.473</t>
+          <t>472785.125715</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.436</t>
+          <t>436496.1997214</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.473</t>
+          <t>472981.72865</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>0.583</t>
+          <t>582971.528112</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0.678</t>
+          <t>677672.58636</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>0.705</t>
+          <t>704701.80207</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>0.765</t>
+          <t>765462.762275</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>0.895</t>
+          <t>895474.375005</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>0.967</t>
+          <t>966660.987216</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>0.777</t>
+          <t>776644.490232</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>0.881</t>
+          <t>881199.643092</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>1.026</t>
+          <t>1026105.259386</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>0.988</t>
+          <t>987678.354841</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1030249.851996</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>1.018</t>
+          <t>1018189.4674441</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>0.573</t>
+          <t>573083.38040896</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.433</t>
+          <t>433009.817203656</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.453</t>
+          <t>453253.996969534</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>0.584</t>
+          <t>583875.87766493</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0.739</t>
+          <t>738903.073891896</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>0.909</t>
+          <t>909018.021570824</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>1.001</t>
+          <t>1001427.87541185</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1230394.04894565</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>1.394</t>
+          <t>1394028.2577365</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>1.151</t>
+          <t>1151168.91465528</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1359962.68281551</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>1.455</t>
+          <t>1455482.26845111</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>1.472</t>
+          <t>1472372.21208569</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>1.531</t>
+          <t>1530674.10028907</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>1.494</t>
+          <t>1494427.53535721</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>0.683</t>
+          <t>682643.217657533</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>599579.2049183</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>619819.031091829</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>0.659</t>
+          <t>658700.767040502</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0.764</t>
+          <t>764161.031655796</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>829976.031336463</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>0.881</t>
+          <t>881079.862285205</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>0.938</t>
+          <t>937700.931733756</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>989540.692324777</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>0.855</t>
+          <t>855193.651850283</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1059649.95891537</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>1.187</t>
+          <t>1187098.9342927</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>1.181</t>
+          <t>1181257.17566016</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>1.194</t>
+          <t>1193656.02955996</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>1.221</t>
+          <t>1220628.55637513</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>18.565</t>
+          <t>18564550</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>18.863</t>
+          <t>18863118</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>19.175</t>
+          <t>19175007</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>20.135</t>
+          <t>20135087</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>21.697</t>
+          <t>21697287</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>23.515</t>
+          <t>23514906</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>24.888</t>
+          <t>24887955</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>26.151</t>
+          <t>26151311</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>26.826</t>
+          <t>26825683</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>24.657</t>
+          <t>24657234</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>26.094</t>
+          <t>26093505</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>27.536</t>
+          <t>27535973</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>28.663</t>
+          <t>28663254</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>29.572</t>
+          <t>29571550</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>30.971</t>
+          <t>30971023</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>6.282</t>
+          <t>6282373.40824366</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>6.238</t>
+          <t>6238270.61609571</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>6.102</t>
+          <t>6101632.58173948</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>6.966</t>
+          <t>6965917.30344096</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>8.386</t>
+          <t>8386045.57491782</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>10.238</t>
+          <t>10238049.620376</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>12.034</t>
+          <t>12034154.3281908</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>14.426</t>
+          <t>14425536.2949305</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>17.207</t>
+          <t>17207030.3041438</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>16.121</t>
+          <t>16121440.6048166</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>18.942</t>
+          <t>18942147.6317154</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>21.914</t>
+          <t>21913614.9280403</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>23.81</t>
+          <t>23810255.6391664</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>24.993</t>
+          <t>24992542.1349743</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>25.61</t>
+          <t>25610236.5866257</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>62.23</t>
+          <t>62229753.3193865</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>61.605</t>
+          <t>61604960.2125258</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>63.686</t>
+          <t>63685981.2160894</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>71.977</t>
+          <t>71977032.6483746</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>82.077</t>
+          <t>82076833.9959776</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>90.664</t>
+          <t>90663628.2520401</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>99.536</t>
+          <t>99535949.1494322</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>113.719</t>
+          <t>113719038.465387</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>126.935</t>
+          <t>126934817.736997</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>117.37</t>
+          <t>117369540.767418</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>130.256</t>
+          <t>130255885.319046</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>147.275</t>
+          <t>147274986.659704</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>151.14</t>
+          <t>151139918.668272</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>156.583</t>
+          <t>156582791.006788</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>160.997</t>
+          <t>160997197.961565</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4337,84 +4342,84 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>37083.09416</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>39465.1509445828</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>45977.3466223032</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>60003.324960004</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>72910.0751952982</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>80749.9531516706</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>90930.500567504</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>109151.911487152</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>0.127</t>
+          <t>127195.753066674</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>109795.537316528</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>0.101</t>
+          <t>101456.362365074</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>0.108</t>
+          <t>108097.178513553</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>97843.0746179348</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>0.099</t>
+          <t>98723.9680275546</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>97418.5872655664</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4424,84 +4429,84 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>0.526</t>
+          <t>526268.540498316</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>0.539</t>
+          <t>539312.73068399</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>590382.851847539</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>0.685</t>
+          <t>685264.780212253</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>0.773</t>
+          <t>773286.464113235</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>0.807</t>
+          <t>806794.705256368</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>0.852</t>
+          <t>852014.304657695</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>0.954</t>
+          <t>954347.867043238</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>1.114</t>
+          <t>1113686.14605307</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>1.083</t>
+          <t>1082598.6718767</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>1.154</t>
+          <t>1153707.31813328</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>1.382</t>
+          <t>1381729.93724796</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>1.328</t>
+          <t>1327569.4702692</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>1.364</t>
+          <t>1363645.05879035</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>1.399</t>
+          <t>1398665.13522947</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4511,84 +4516,84 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>0.277</t>
+          <t>277219.052132</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>0.284</t>
+          <t>283967.45162</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>0.322</t>
+          <t>322105.353592</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>0.371</t>
+          <t>371147.840972</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>0.427</t>
+          <t>427152.010912</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>0.495</t>
+          <t>495268.35504</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>559533.699036</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>0.668</t>
+          <t>668111.836196</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>0.779</t>
+          <t>779494.002248</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>0.647</t>
+          <t>646524.762065</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>0.701</t>
+          <t>700849.568606</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>0.816</t>
+          <t>815806.182</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>0.833</t>
+          <t>832712.786136</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>0.858</t>
+          <t>858418.687865</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>0.835</t>
+          <t>835078.908764</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4600,7 +4605,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4612,7 +4617,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4624,7 +4629,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4636,7 +4641,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4648,7 +4653,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4695,6 +4700,11 @@
           <t>gross_output.s.us</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4729,6 +4739,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>WIOD16</t>
